--- a/Final_Figures_and_Sheets_Singleset/Kd_pc_values_CDR3a.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kd_pc_values_CDR3a.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J723"/>
+  <dimension ref="A1:J725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,8 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -524,8 +523,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -565,8 +563,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -606,8 +603,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -647,8 +643,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -688,8 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -729,8 +723,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -770,8 +763,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -811,8 +803,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -852,8 +843,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -893,8 +883,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -934,8 +923,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -975,8 +963,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1016,8 +1003,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1057,8 +1043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1098,8 +1083,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1139,8 +1123,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1180,8 +1163,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1221,8 +1203,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1262,8 +1243,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1303,8 +1283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1344,8 +1323,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1385,8 +1363,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1426,8 +1403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1467,8 +1443,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1508,8 +1483,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1549,8 +1523,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1590,8 +1563,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1633,8 +1605,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1676,8 +1647,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1719,8 +1689,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1762,8 +1731,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1805,8 +1773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1848,8 +1815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1891,8 +1857,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1934,8 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1977,8 +1941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2020,8 +1983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2063,8 +2025,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2106,8 +2067,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2149,8 +2109,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2192,8 +2151,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2235,8 +2193,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2278,8 +2235,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2321,8 +2277,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2364,8 +2319,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2407,8 +2361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2450,8 +2403,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2493,8 +2445,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2536,8 +2487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2579,8 +2529,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2622,8 +2571,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2665,8 +2613,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2708,8 +2655,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2751,8 +2697,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2794,8 +2739,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2837,8 +2781,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2880,8 +2823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2923,8 +2865,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2966,8 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -3009,8 +2949,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -3052,8 +2991,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3095,8 +3033,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3138,8 +3075,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3173,8 +3109,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3208,8 +3143,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3243,8 +3177,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3278,8 +3211,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3313,8 +3245,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3348,8 +3279,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3383,8 +3313,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3418,8 +3347,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3453,8 +3381,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3488,8 +3415,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3523,8 +3449,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3558,8 +3483,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3593,8 +3517,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3628,8 +3551,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3663,8 +3585,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3698,8 +3619,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3733,8 +3653,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3768,8 +3687,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3803,8 +3721,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3838,8 +3755,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3873,8 +3789,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3908,8 +3823,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3943,8 +3857,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3978,8 +3891,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4013,8 +3925,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4048,8 +3959,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4083,8 +3993,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4118,8 +4027,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4153,8 +4061,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4188,8 +4095,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4223,8 +4129,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4258,8 +4163,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4293,8 +4197,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4328,8 +4231,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4363,8 +4265,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4398,8 +4299,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4433,8 +4333,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4468,8 +4367,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4503,8 +4401,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4538,8 +4435,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4573,8 +4469,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4608,8 +4503,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4643,8 +4537,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4678,8 +4571,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4713,8 +4605,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4748,8 +4639,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4783,8 +4673,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4818,8 +4707,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4853,8 +4741,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4888,8 +4775,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4923,8 +4809,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4958,8 +4843,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4993,8 +4877,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5028,8 +4911,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5063,8 +4945,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5098,8 +4979,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5133,8 +5013,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5168,8 +5047,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5203,8 +5081,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5238,8 +5115,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5273,8 +5149,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5308,8 +5183,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5343,8 +5217,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5378,8 +5251,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5413,8 +5285,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5448,8 +5319,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5483,8 +5353,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5518,8 +5387,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5553,8 +5421,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5588,8 +5455,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5623,8 +5489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5658,8 +5523,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5693,8 +5557,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5728,8 +5591,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5763,8 +5625,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5798,8 +5659,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5833,8 +5693,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5868,8 +5727,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5903,8 +5761,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5938,8 +5795,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5973,8 +5829,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -6008,8 +5863,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -6043,8 +5897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6078,8 +5931,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6113,8 +5965,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6148,8 +5999,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6183,8 +6033,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6218,8 +6067,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6253,8 +6101,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6288,8 +6135,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6323,8 +6169,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6358,8 +6203,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6393,8 +6237,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6428,8 +6271,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6463,8 +6305,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6498,8 +6339,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6533,8 +6373,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6568,8 +6407,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6603,8 +6441,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6638,8 +6475,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6673,8 +6509,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6708,8 +6543,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6743,8 +6577,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6778,8 +6611,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6813,8 +6645,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6848,8 +6679,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6883,8 +6713,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6918,8 +6747,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6953,8 +6781,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6988,8 +6815,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -7023,8 +6849,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7058,8 +6883,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -7093,8 +6917,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -7128,8 +6951,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -7163,8 +6985,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -7198,8 +7019,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7233,8 +7053,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7268,8 +7087,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7303,8 +7121,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7338,8 +7155,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -7373,8 +7189,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -7408,8 +7223,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -7443,8 +7257,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -7478,8 +7291,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7513,8 +7325,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -7548,8 +7359,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7583,8 +7393,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7618,8 +7427,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -7653,8 +7461,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -7688,8 +7495,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -7723,8 +7529,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -7758,8 +7563,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -7793,8 +7597,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -7828,8 +7631,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -7863,8 +7665,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -7898,8 +7699,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -7933,8 +7733,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -7968,8 +7767,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -8003,8 +7801,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -8038,8 +7835,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -8073,8 +7869,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8108,8 +7903,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -8143,8 +7937,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -8178,8 +7971,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -8213,8 +8005,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -8248,8 +8039,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -8283,8 +8073,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -8318,8 +8107,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -8353,8 +8141,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -8388,8 +8175,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -8423,8 +8209,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -8458,8 +8243,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -8493,8 +8277,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -8528,8 +8311,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -8563,8 +8345,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -8598,8 +8379,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -8633,8 +8413,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -8668,8 +8447,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -8703,8 +8481,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -8738,8 +8515,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -8773,8 +8549,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -8808,8 +8583,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -8843,8 +8617,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -8878,8 +8651,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -8913,8 +8685,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -8948,8 +8719,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -8983,8 +8753,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -9018,8 +8787,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -9053,8 +8821,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -9088,8 +8855,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -9123,8 +8889,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -9158,8 +8923,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -9193,8 +8957,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -9228,8 +8991,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -9263,8 +9025,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -9298,8 +9059,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -9333,8 +9093,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -9368,8 +9127,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -9403,8 +9161,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -9438,8 +9195,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -9473,8 +9229,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -9508,8 +9263,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -9543,8 +9297,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -9578,8 +9331,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9613,8 +9365,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9648,8 +9399,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -9683,8 +9433,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -9718,8 +9467,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -9753,8 +9501,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -9788,8 +9535,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -9823,8 +9569,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -9858,8 +9603,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -9893,8 +9637,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -9928,8 +9671,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -9963,8 +9705,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -9998,8 +9739,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -10033,8 +9773,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -10068,8 +9807,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -10103,8 +9841,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -10138,8 +9875,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -10173,8 +9909,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -10208,8 +9943,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -10243,8 +9977,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -10278,8 +10011,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -10313,8 +10045,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -10348,8 +10079,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -10383,8 +10113,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -10418,8 +10147,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -10453,8 +10181,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -10488,8 +10215,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -10523,8 +10249,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -10558,8 +10283,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -10593,8 +10317,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -10628,8 +10351,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -10663,8 +10385,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -10698,8 +10419,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -10733,8 +10453,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -10768,8 +10487,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -10803,8 +10521,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -10838,8 +10555,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -10873,8 +10589,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -10908,8 +10623,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -10943,8 +10657,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -10978,8 +10691,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -11013,8 +10725,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -11048,8 +10759,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -11083,8 +10793,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -11118,8 +10827,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -11153,8 +10861,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -11188,8 +10895,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -11223,8 +10929,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -11258,8 +10963,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -11293,8 +10997,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -11328,8 +11031,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -11363,8 +11065,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -11398,8 +11099,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -11433,8 +11133,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -11468,8 +11167,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -11503,8 +11201,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -11538,8 +11235,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -11573,8 +11269,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -11608,8 +11303,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -11643,8 +11337,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -11678,8 +11371,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -11713,8 +11405,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -11748,8 +11439,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -11783,8 +11473,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -11818,8 +11507,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -11853,8 +11541,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -11888,8 +11575,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -11923,8 +11609,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -11958,8 +11643,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -11993,8 +11677,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -12028,8 +11711,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -12063,8 +11745,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -12098,8 +11779,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -12133,8 +11813,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -12168,8 +11847,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -12203,8 +11881,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -12238,8 +11915,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -12273,8 +11949,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -12308,8 +11983,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -12343,8 +12017,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -12378,8 +12051,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -12413,8 +12085,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -12448,8 +12119,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -12483,8 +12153,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -12518,8 +12187,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -12553,8 +12221,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -12588,8 +12255,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -12623,8 +12289,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -12658,8 +12323,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -12693,8 +12357,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -12728,8 +12391,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -12763,8 +12425,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -12798,8 +12459,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -12833,8 +12493,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -12868,8 +12527,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -12903,8 +12561,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -12938,8 +12595,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -12973,8 +12629,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -13008,8 +12663,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -13043,8 +12697,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -13078,8 +12731,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -13113,8 +12765,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -13148,8 +12799,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -13183,8 +12833,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -13218,8 +12867,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -13253,8 +12901,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -13288,8 +12935,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -13323,8 +12969,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -13358,8 +13003,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -13393,8 +13037,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -13428,8 +13071,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -13463,8 +13105,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -13498,8 +13139,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -13533,8 +13173,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -13568,8 +13207,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -13603,8 +13241,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -13638,8 +13275,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -13673,8 +13309,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -13708,8 +13343,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -13743,8 +13377,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -13778,8 +13411,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -13813,8 +13445,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -13848,8 +13479,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -13879,8 +13509,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -13910,8 +13539,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -13941,8 +13569,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -13972,8 +13599,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -14003,8 +13629,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -14034,8 +13659,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -14065,8 +13689,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -14096,8 +13719,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -14127,8 +13749,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -14158,8 +13779,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -14189,8 +13809,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -14220,8 +13839,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -14251,8 +13869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -14282,8 +13899,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -14313,8 +13929,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -14344,8 +13959,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -14375,8 +13989,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -14406,8 +14019,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -14437,8 +14049,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -14468,8 +14079,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -14499,8 +14109,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -14530,8 +14139,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -14561,8 +14169,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -14592,8 +14199,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -14623,8 +14229,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -14654,8 +14259,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -14685,8 +14289,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -14716,8 +14319,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -14747,8 +14349,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -14778,8 +14379,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -14809,8 +14409,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -14840,8 +14439,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -14871,8 +14469,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -14902,8 +14499,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -14933,8 +14529,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -14964,8 +14559,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -14995,8 +14589,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -15026,8 +14619,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -15057,8 +14649,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -15088,8 +14679,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -15119,8 +14709,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -15150,8 +14739,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -15181,8 +14769,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -15212,8 +14799,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -15243,8 +14829,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -15274,8 +14859,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -15305,8 +14889,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -15336,8 +14919,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -15367,8 +14949,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -15398,8 +14979,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -15429,8 +15009,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -15460,8 +15039,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -15491,8 +15069,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -15522,8 +15099,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -15553,8 +15129,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15584,8 +15159,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -15615,8 +15189,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -15646,8 +15219,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15677,8 +15249,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -15708,8 +15279,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -15739,8 +15309,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -15770,8 +15339,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -15801,8 +15369,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -15832,8 +15399,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -15863,8 +15429,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -15894,8 +15459,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -15925,8 +15489,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -15956,8 +15519,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -15987,8 +15549,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -16018,8 +15579,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -16049,8 +15609,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -16080,8 +15639,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -16111,8 +15669,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -16142,8 +15699,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -16173,8 +15729,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -16204,8 +15759,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -16235,8 +15789,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -16266,8 +15819,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -16297,8 +15849,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -16328,8 +15879,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -16359,8 +15909,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -16390,8 +15939,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -16421,8 +15969,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -16452,8 +15999,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -16483,8 +16029,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16514,8 +16059,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -16545,8 +16089,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -16576,8 +16119,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -16607,8 +16149,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -16638,8 +16179,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -16669,8 +16209,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -16700,8 +16239,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -16731,8 +16269,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -16762,8 +16299,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -16793,8 +16329,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -16824,8 +16359,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -16855,8 +16389,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -16886,8 +16419,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -16917,8 +16449,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -16948,8 +16479,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -16979,8 +16509,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -17010,8 +16539,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -17041,8 +16569,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -17072,8 +16599,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -17103,8 +16629,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -17134,8 +16659,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -17165,8 +16689,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -17196,8 +16719,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -17227,8 +16749,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -17258,8 +16779,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -17289,8 +16809,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -17320,8 +16839,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -17351,8 +16869,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -17382,8 +16899,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -17413,8 +16929,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -17444,8 +16959,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -17475,8 +16989,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -17506,8 +17019,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -17537,8 +17049,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -17568,8 +17079,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -17599,8 +17109,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -17630,8 +17139,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -17661,8 +17169,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -17692,8 +17199,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -17723,8 +17229,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -17754,8 +17259,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -17785,8 +17289,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -17816,8 +17319,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -17847,8 +17349,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -17878,8 +17379,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -17909,8 +17409,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -17940,8 +17439,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -17971,8 +17469,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -18002,8 +17499,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -18033,8 +17529,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
@@ -18064,8 +17559,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -18095,8 +17589,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
@@ -18126,8 +17619,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
@@ -18157,8 +17649,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -18188,8 +17679,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
@@ -18219,8 +17709,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
@@ -18250,8 +17739,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -18281,8 +17769,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
@@ -18312,8 +17799,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
@@ -18343,8 +17829,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -18374,8 +17859,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
@@ -18405,8 +17889,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
@@ -18436,8 +17919,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -18467,8 +17949,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
@@ -18498,8 +17979,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
@@ -18529,8 +18009,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -18560,8 +18039,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -18591,8 +18069,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -18622,8 +18099,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -18653,8 +18129,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -18684,8 +18159,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -18715,8 +18189,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -18746,8 +18219,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -18777,8 +18249,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
@@ -18808,8 +18279,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -18839,8 +18309,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -18870,8 +18339,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B533" t="inlineStr"/>
@@ -18901,8 +18369,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -18932,8 +18399,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B535" t="inlineStr"/>
@@ -18963,8 +18429,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B536" t="inlineStr"/>
@@ -18994,8 +18459,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -19025,8 +18489,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -19056,8 +18519,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
@@ -19087,8 +18549,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -19118,8 +18579,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
@@ -19149,8 +18609,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
@@ -19180,8 +18639,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -19211,8 +18669,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
@@ -19242,8 +18699,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B545" t="inlineStr"/>
@@ -19273,8 +18729,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -19304,8 +18759,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B547" t="inlineStr"/>
@@ -19335,8 +18789,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
@@ -19366,8 +18819,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -19397,8 +18849,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B550" t="inlineStr"/>
@@ -19428,8 +18879,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B551" t="inlineStr"/>
@@ -19459,8 +18909,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -19490,8 +18939,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B553" t="inlineStr"/>
@@ -19521,8 +18969,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B554" t="inlineStr"/>
@@ -19552,8 +18999,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -19583,8 +19029,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
@@ -19614,8 +19059,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
@@ -19645,8 +19089,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -19676,8 +19119,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
@@ -19707,8 +19149,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
@@ -19738,8 +19179,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -19769,8 +19209,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
@@ -19800,8 +19239,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
@@ -19831,8 +19269,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -19862,8 +19299,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
@@ -19893,8 +19329,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
@@ -19924,8 +19359,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
@@ -19955,8 +19389,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
@@ -19986,8 +19419,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
@@ -20017,8 +19449,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
@@ -20048,8 +19479,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
@@ -20079,8 +19509,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
@@ -20110,8 +19539,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
@@ -20141,8 +19569,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B574" t="inlineStr"/>
@@ -20172,8 +19599,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
@@ -20203,8 +19629,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
@@ -20234,8 +19659,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
@@ -20265,8 +19689,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B578" t="inlineStr"/>
@@ -20296,8 +19719,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -20327,8 +19749,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
@@ -20358,8 +19779,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
@@ -20389,8 +19809,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
@@ -20420,8 +19839,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
@@ -20451,8 +19869,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
@@ -20482,8 +19899,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -20513,8 +19929,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
@@ -20544,8 +19959,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
@@ -20575,8 +19989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -20606,8 +20019,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B589" t="inlineStr"/>
@@ -20637,8 +20049,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -20668,8 +20079,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -20699,8 +20109,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -20730,8 +20139,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
@@ -20761,8 +20169,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -20792,8 +20199,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
@@ -20823,8 +20229,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B596" t="inlineStr"/>
@@ -20854,8 +20259,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -20885,8 +20289,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -20916,8 +20319,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -20947,8 +20349,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -20978,8 +20379,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -21009,8 +20409,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -21040,8 +20439,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -21071,8 +20469,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -21102,8 +20499,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -21133,8 +20529,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -21164,8 +20559,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -21195,8 +20589,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -21226,8 +20619,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -21257,8 +20649,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
@@ -21288,8 +20679,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
@@ -21319,8 +20709,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -21350,8 +20739,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
@@ -21381,8 +20769,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
@@ -21412,8 +20799,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -21443,8 +20829,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
@@ -21474,8 +20859,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
@@ -21505,8 +20889,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -21536,8 +20919,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
@@ -21567,8 +20949,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
@@ -21598,8 +20979,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -21629,8 +21009,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
@@ -21660,8 +21039,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
@@ -21691,8 +21069,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -21722,8 +21099,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
@@ -21753,8 +21129,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B626" t="inlineStr"/>
@@ -21784,8 +21159,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -21815,8 +21189,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
@@ -21846,8 +21219,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
@@ -21877,8 +21249,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -21908,8 +21279,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
@@ -21939,8 +21309,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
@@ -21970,8 +21339,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -22001,8 +21369,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
@@ -22032,8 +21399,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
@@ -22063,8 +21429,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
@@ -22094,8 +21459,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B637" t="inlineStr"/>
@@ -22125,8 +21489,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B638" t="inlineStr"/>
@@ -22156,8 +21519,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B639" t="inlineStr"/>
@@ -22187,8 +21549,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B640" t="inlineStr"/>
@@ -22218,8 +21579,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
@@ -22249,8 +21609,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
@@ -22280,8 +21639,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
@@ -22311,8 +21669,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
@@ -22342,8 +21699,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B645" t="inlineStr"/>
@@ -22373,8 +21729,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B646" t="inlineStr"/>
@@ -22404,8 +21759,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B647" t="inlineStr"/>
@@ -22435,8 +21789,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -22466,8 +21819,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B649" t="inlineStr"/>
@@ -22497,8 +21849,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B650" t="inlineStr"/>
@@ -22528,8 +21879,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -22559,8 +21909,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B652" t="inlineStr"/>
@@ -22590,8 +21939,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B653" t="inlineStr"/>
@@ -22621,8 +21969,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -22652,8 +21999,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B655" t="inlineStr"/>
@@ -22683,8 +22029,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -22714,8 +22059,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -22745,8 +22089,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B658" t="inlineStr"/>
@@ -22776,8 +22119,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B659" t="inlineStr"/>
@@ -22807,8 +22149,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -22838,8 +22179,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -22869,8 +22209,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B662" t="inlineStr"/>
@@ -22900,8 +22239,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -22931,8 +22269,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B664" t="inlineStr"/>
@@ -22962,8 +22299,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B665" t="inlineStr"/>
@@ -22993,8 +22329,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B666" t="inlineStr"/>
@@ -23024,8 +22359,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B667" t="inlineStr"/>
@@ -23055,8 +22389,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B668" t="inlineStr"/>
@@ -23086,8 +22419,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B669" t="inlineStr"/>
@@ -23117,8 +22449,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B670" t="inlineStr"/>
@@ -23148,8 +22479,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B671" t="inlineStr"/>
@@ -23179,8 +22509,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B672" t="inlineStr"/>
@@ -23210,8 +22539,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B673" t="inlineStr"/>
@@ -23241,8 +22569,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B674" t="inlineStr"/>
@@ -23272,8 +22599,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B675" t="inlineStr"/>
@@ -23303,8 +22629,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B676" t="inlineStr"/>
@@ -23334,8 +22659,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B677" t="inlineStr"/>
@@ -23365,8 +22689,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
@@ -23396,8 +22719,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
@@ -23427,8 +22749,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B680" t="inlineStr"/>
@@ -23458,8 +22779,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
@@ -23489,8 +22809,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B682" t="inlineStr"/>
@@ -23520,8 +22839,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B683" t="inlineStr"/>
@@ -23551,8 +22869,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
@@ -23582,8 +22899,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B685" t="inlineStr"/>
@@ -23613,8 +22929,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B686" t="inlineStr"/>
@@ -23644,8 +22959,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
@@ -23675,8 +22989,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B688" t="inlineStr"/>
@@ -23706,8 +23019,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B689" t="inlineStr"/>
@@ -23737,8 +23049,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -23768,8 +23079,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B691" t="inlineStr"/>
@@ -23799,8 +23109,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B692" t="inlineStr"/>
@@ -23830,8 +23139,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -23861,8 +23169,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B694" t="inlineStr"/>
@@ -23892,8 +23199,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B695" t="inlineStr"/>
@@ -23923,8 +23229,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B696" t="inlineStr"/>
@@ -23954,8 +23259,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B697" t="inlineStr"/>
@@ -23985,8 +23289,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B698" t="inlineStr"/>
@@ -24016,8 +23319,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B699" t="inlineStr"/>
@@ -24047,8 +23349,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B700" t="inlineStr"/>
@@ -24078,8 +23379,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B701" t="inlineStr"/>
@@ -24109,8 +23409,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -24140,8 +23439,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B703" t="inlineStr"/>
@@ -24171,8 +23469,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B704" t="inlineStr"/>
@@ -24202,8 +23499,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B705" t="inlineStr"/>
@@ -24233,8 +23529,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B706" t="inlineStr"/>
@@ -24264,8 +23559,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B707" t="inlineStr"/>
@@ -24295,8 +23589,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B708" t="inlineStr"/>
@@ -24326,8 +23619,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B709" t="inlineStr"/>
@@ -24357,8 +23649,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B710" t="inlineStr"/>
@@ -24388,8 +23679,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B711" t="inlineStr"/>
@@ -24419,8 +23709,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B712" t="inlineStr"/>
@@ -24450,8 +23739,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B713" t="inlineStr"/>
@@ -24481,8 +23769,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B714" t="inlineStr"/>
@@ -24512,8 +23799,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B715" t="inlineStr"/>
@@ -24543,8 +23829,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B716" t="inlineStr"/>
@@ -24574,8 +23859,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
@@ -24605,8 +23889,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B718" t="inlineStr"/>
@@ -24636,8 +23919,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B719" t="inlineStr"/>
@@ -24667,8 +23949,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
@@ -24698,8 +23979,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B721" t="inlineStr"/>
@@ -24729,8 +24009,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Pre-Immune
-Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B722" t="inlineStr"/>
@@ -24747,7 +24026,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Pre-Immune</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="I722" t="inlineStr"/>
@@ -24756,8 +24035,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Pre-Immune
-Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
@@ -24774,11 +24052,63 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Pre-Immune</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="I723" t="inlineStr"/>
       <c r="J723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr"/>
+      <c r="C724" t="inlineStr"/>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="n">
+        <v>7.68672735770055e-05</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>B10BR Kb × B10BR Kd</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>B10BR Kb × B10BR Kd</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr"/>
+      <c r="C725" t="inlineStr"/>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="n">
+        <v>8.978999592653821e-05</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>B10BR SLO × C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>B10BR SLO × C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Figures_and_Sheets_Singleset/Kd_pc_values_CDR3a.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kd_pc_values_CDR3a.xlsx
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2403,7 +2403,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3177,7 +3177,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3313,7 +3313,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3653,7 +3653,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3823,7 +3823,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3857,7 +3857,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3891,7 +3891,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3925,7 +3925,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3959,7 +3959,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3993,7 +3993,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4027,7 +4027,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4367,7 +4367,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4401,7 +4401,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4537,7 +4537,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4673,7 +4673,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4809,7 +4809,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4843,7 +4843,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4911,7 +4911,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4945,7 +4945,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5353,7 +5353,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5421,7 +5421,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5455,7 +5455,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5489,7 +5489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5523,7 +5523,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5557,7 +5557,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5591,7 +5591,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5693,7 +5693,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5761,7 +5761,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5795,7 +5795,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5829,7 +5829,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5863,7 +5863,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5965,7 +5965,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6067,7 +6067,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6237,7 +6237,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6271,7 +6271,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6441,7 +6441,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6475,7 +6475,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6543,7 +6543,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6577,7 +6577,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6611,7 +6611,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6645,7 +6645,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6713,7 +6713,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6747,7 +6747,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -6917,7 +6917,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -6951,7 +6951,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -6985,7 +6985,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7053,7 +7053,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7087,7 +7087,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7121,7 +7121,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -7189,7 +7189,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -7291,7 +7291,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -7359,7 +7359,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7427,7 +7427,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -7461,7 +7461,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -7495,7 +7495,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -7529,7 +7529,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -7733,7 +7733,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -7835,7 +7835,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -7869,7 +7869,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -7903,7 +7903,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -7937,7 +7937,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -8005,7 +8005,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -8073,7 +8073,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -8107,7 +8107,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -8141,7 +8141,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -8209,7 +8209,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -8243,7 +8243,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -8379,7 +8379,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -8413,7 +8413,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -8481,7 +8481,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -8515,7 +8515,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -8549,7 +8549,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -8583,7 +8583,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -8719,7 +8719,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -8753,7 +8753,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -8821,7 +8821,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -8855,7 +8855,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -8889,7 +8889,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -8923,7 +8923,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -8991,7 +8991,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -9025,7 +9025,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -9059,7 +9059,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -9127,7 +9127,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -9161,7 +9161,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -9195,7 +9195,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -9229,7 +9229,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -9297,7 +9297,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -9331,7 +9331,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9365,7 +9365,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9399,7 +9399,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -9433,7 +9433,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -9467,7 +9467,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -9501,7 +9501,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -9535,7 +9535,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -9569,7 +9569,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -9637,7 +9637,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -9671,7 +9671,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -9705,7 +9705,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -9841,7 +9841,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -9943,7 +9943,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -9977,7 +9977,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -10045,7 +10045,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -10079,7 +10079,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -10113,7 +10113,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -10147,7 +10147,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -10181,7 +10181,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -10215,7 +10215,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -10283,7 +10283,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -10317,7 +10317,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -10351,7 +10351,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -10385,7 +10385,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -10419,7 +10419,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -10453,7 +10453,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -10487,7 +10487,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -10521,7 +10521,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -10589,7 +10589,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -10623,7 +10623,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -10657,7 +10657,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -10691,7 +10691,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -10725,7 +10725,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -10759,7 +10759,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -10827,7 +10827,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -10963,7 +10963,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -10997,7 +10997,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -11031,7 +11031,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -11065,7 +11065,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -11099,7 +11099,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -11133,7 +11133,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -11167,7 +11167,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -11235,7 +11235,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -11269,7 +11269,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -11303,7 +11303,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -11337,7 +11337,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -11371,7 +11371,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -11405,7 +11405,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -11439,7 +11439,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -11473,7 +11473,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -11507,7 +11507,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -11575,7 +11575,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -11609,7 +11609,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -11643,7 +11643,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -11711,7 +11711,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -11745,7 +11745,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -11779,7 +11779,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -11813,7 +11813,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -11881,7 +11881,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -11915,7 +11915,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -11949,7 +11949,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -11983,7 +11983,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -12017,7 +12017,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -12085,7 +12085,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -12119,7 +12119,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -12153,7 +12153,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -12221,7 +12221,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -12255,7 +12255,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -12289,7 +12289,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -12357,7 +12357,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -12391,7 +12391,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -12425,7 +12425,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -12459,7 +12459,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -12561,7 +12561,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -12595,7 +12595,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -12629,7 +12629,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -12663,7 +12663,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -12697,7 +12697,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -12731,7 +12731,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -12765,7 +12765,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -12799,7 +12799,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -12901,7 +12901,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -12935,7 +12935,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -12969,7 +12969,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -13003,7 +13003,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -13037,7 +13037,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -13071,7 +13071,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -13105,7 +13105,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -13173,7 +13173,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -13207,7 +13207,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -13241,7 +13241,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -13275,7 +13275,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -13309,7 +13309,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -13343,7 +13343,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -13377,7 +13377,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -13411,7 +13411,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -13445,7 +13445,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -13509,7 +13509,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -13599,7 +13599,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -13629,7 +13629,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -13659,7 +13659,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -13689,7 +13689,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -13719,7 +13719,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -13749,7 +13749,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -13809,7 +13809,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -13839,7 +13839,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -13869,7 +13869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -13929,7 +13929,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -13959,7 +13959,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -14019,7 +14019,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -14079,7 +14079,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -14139,7 +14139,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -14169,7 +14169,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -14199,7 +14199,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -14259,7 +14259,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -14289,7 +14289,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -14319,7 +14319,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -14349,7 +14349,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -14379,7 +14379,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -14499,7 +14499,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -14529,7 +14529,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -14559,7 +14559,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -14589,7 +14589,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -14649,7 +14649,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -14709,7 +14709,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -14739,7 +14739,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -14769,7 +14769,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -14829,7 +14829,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -14859,7 +14859,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -14919,7 +14919,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -14949,7 +14949,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -14979,7 +14979,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -15009,7 +15009,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -15069,7 +15069,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -15099,7 +15099,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -15129,7 +15129,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15159,7 +15159,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -15219,7 +15219,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15249,7 +15249,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -15309,7 +15309,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -15339,7 +15339,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -15369,7 +15369,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -15399,7 +15399,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -15429,7 +15429,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -15459,7 +15459,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -15489,7 +15489,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -15519,7 +15519,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -15549,7 +15549,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -15579,7 +15579,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -15639,7 +15639,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -15669,7 +15669,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -15699,7 +15699,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -15729,7 +15729,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -15789,7 +15789,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -15819,7 +15819,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -15849,7 +15849,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -15879,7 +15879,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -15909,7 +15909,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -15939,7 +15939,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -15969,7 +15969,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -15999,7 +15999,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -16029,7 +16029,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16059,7 +16059,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -16089,7 +16089,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -16119,7 +16119,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -16149,7 +16149,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -16209,7 +16209,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -16239,7 +16239,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -16269,7 +16269,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -16299,7 +16299,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -16359,7 +16359,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -16389,7 +16389,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -16419,7 +16419,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -16449,7 +16449,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -16509,7 +16509,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -16569,7 +16569,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -16599,7 +16599,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -16629,7 +16629,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -16659,7 +16659,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -16689,7 +16689,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -16719,7 +16719,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -16779,7 +16779,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -16809,7 +16809,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -16839,7 +16839,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -16869,7 +16869,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -16929,7 +16929,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -16959,7 +16959,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -16989,7 +16989,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -17019,7 +17019,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -17049,7 +17049,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -17079,7 +17079,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -17109,7 +17109,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -17139,7 +17139,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -17169,7 +17169,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -17199,7 +17199,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -17229,7 +17229,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -17259,7 +17259,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -17289,7 +17289,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -17349,7 +17349,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -17379,7 +17379,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -17409,7 +17409,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -17499,7 +17499,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -17529,7 +17529,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
@@ -17559,7 +17559,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -17589,7 +17589,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
@@ -17619,7 +17619,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -17679,7 +17679,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
@@ -17709,7 +17709,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
@@ -17739,7 +17739,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
@@ -17799,7 +17799,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
@@ -17829,7 +17829,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -17859,7 +17859,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
@@ -17919,7 +17919,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -17949,7 +17949,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
@@ -17979,7 +17979,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
@@ -18009,7 +18009,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -18069,7 +18069,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -18099,7 +18099,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -18129,7 +18129,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -18159,7 +18159,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -18189,7 +18189,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -18219,7 +18219,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -18249,7 +18249,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
@@ -18279,7 +18279,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -18309,7 +18309,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -18339,7 +18339,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B533" t="inlineStr"/>
@@ -18369,7 +18369,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -18399,7 +18399,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B535" t="inlineStr"/>
@@ -18429,7 +18429,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B536" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -18489,7 +18489,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -18519,7 +18519,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
@@ -18549,7 +18549,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -18579,7 +18579,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
@@ -18639,7 +18639,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -18669,7 +18669,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
@@ -18699,7 +18699,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B545" t="inlineStr"/>
@@ -18729,7 +18729,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -18759,7 +18759,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B547" t="inlineStr"/>
@@ -18789,7 +18789,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
@@ -18819,7 +18819,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -18849,7 +18849,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B550" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B551" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B553" t="inlineStr"/>
@@ -18969,7 +18969,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B554" t="inlineStr"/>
@@ -18999,7 +18999,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
@@ -19059,7 +19059,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
@@ -19089,7 +19089,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -19119,7 +19119,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
@@ -19149,7 +19149,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
@@ -19179,7 +19179,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -19209,7 +19209,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
@@ -19269,7 +19269,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -19299,7 +19299,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
@@ -19329,7 +19329,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
@@ -19359,7 +19359,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
@@ -19389,7 +19389,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
@@ -19419,7 +19419,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
@@ -19449,7 +19449,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
@@ -19509,7 +19509,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
@@ -19539,7 +19539,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
@@ -19569,7 +19569,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B574" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
@@ -19629,7 +19629,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
@@ -19659,7 +19659,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
@@ -19689,7 +19689,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B578" t="inlineStr"/>
@@ -19719,7 +19719,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -19749,7 +19749,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
@@ -19779,7 +19779,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
@@ -19809,7 +19809,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
@@ -19839,7 +19839,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
@@ -19869,7 +19869,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
@@ -19899,7 +19899,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -19929,7 +19929,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
@@ -19959,7 +19959,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
@@ -19989,7 +19989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -20019,7 +20019,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B589" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -20079,7 +20079,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -20109,7 +20109,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -20139,7 +20139,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -20199,7 +20199,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
@@ -20229,7 +20229,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B596" t="inlineStr"/>
@@ -20259,7 +20259,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -20289,7 +20289,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -20319,7 +20319,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -20349,7 +20349,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -20379,7 +20379,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -20409,7 +20409,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -20439,7 +20439,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -20469,7 +20469,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -20499,7 +20499,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -20559,7 +20559,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -20589,7 +20589,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -20649,7 +20649,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
@@ -20679,7 +20679,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
@@ -20709,7 +20709,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -20739,7 +20739,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
@@ -20769,7 +20769,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
@@ -20799,7 +20799,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -20829,7 +20829,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
@@ -20859,7 +20859,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -20919,7 +20919,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
@@ -20949,7 +20949,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
@@ -20979,7 +20979,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -21009,7 +21009,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
@@ -21069,7 +21069,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -21099,7 +21099,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
@@ -21129,7 +21129,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B626" t="inlineStr"/>
@@ -21159,7 +21159,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
@@ -21219,7 +21219,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
@@ -21249,7 +21249,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -21279,7 +21279,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
@@ -21309,7 +21309,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
@@ -21339,7 +21339,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -21369,7 +21369,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
@@ -21429,7 +21429,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
@@ -21459,7 +21459,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B637" t="inlineStr"/>
@@ -21489,7 +21489,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B638" t="inlineStr"/>
@@ -21519,7 +21519,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B639" t="inlineStr"/>
@@ -21549,7 +21549,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B640" t="inlineStr"/>
@@ -21579,7 +21579,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
@@ -21639,7 +21639,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
@@ -21669,7 +21669,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
@@ -21699,7 +21699,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B645" t="inlineStr"/>
@@ -21729,7 +21729,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B646" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B647" t="inlineStr"/>
@@ -21789,7 +21789,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -21819,7 +21819,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B649" t="inlineStr"/>
@@ -21849,7 +21849,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B650" t="inlineStr"/>
@@ -21879,7 +21879,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -21909,7 +21909,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B652" t="inlineStr"/>
@@ -21939,7 +21939,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B653" t="inlineStr"/>
@@ -21969,7 +21969,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B655" t="inlineStr"/>
@@ -22029,7 +22029,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -22059,7 +22059,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -22089,7 +22089,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B658" t="inlineStr"/>
@@ -22119,7 +22119,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B659" t="inlineStr"/>
@@ -22149,7 +22149,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -22209,7 +22209,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B662" t="inlineStr"/>
@@ -22239,7 +22239,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -22269,7 +22269,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B664" t="inlineStr"/>
@@ -22299,7 +22299,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B665" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B666" t="inlineStr"/>
@@ -22359,7 +22359,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B667" t="inlineStr"/>
@@ -22389,7 +22389,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B668" t="inlineStr"/>
@@ -22419,7 +22419,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B669" t="inlineStr"/>
@@ -22449,7 +22449,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B670" t="inlineStr"/>
@@ -22479,7 +22479,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B671" t="inlineStr"/>
@@ -22509,7 +22509,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B672" t="inlineStr"/>
@@ -22539,7 +22539,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B673" t="inlineStr"/>
@@ -22569,7 +22569,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B674" t="inlineStr"/>
@@ -22599,7 +22599,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B675" t="inlineStr"/>
@@ -22629,7 +22629,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B676" t="inlineStr"/>
@@ -22659,7 +22659,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B677" t="inlineStr"/>
@@ -22689,7 +22689,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
@@ -22719,7 +22719,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B680" t="inlineStr"/>
@@ -22779,7 +22779,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
@@ -22809,7 +22809,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B682" t="inlineStr"/>
@@ -22839,7 +22839,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B683" t="inlineStr"/>
@@ -22869,7 +22869,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B685" t="inlineStr"/>
@@ -22929,7 +22929,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B686" t="inlineStr"/>
@@ -22959,7 +22959,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
@@ -22989,7 +22989,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B688" t="inlineStr"/>
@@ -23019,7 +23019,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B689" t="inlineStr"/>
@@ -23049,7 +23049,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -23079,7 +23079,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B691" t="inlineStr"/>
@@ -23109,7 +23109,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B692" t="inlineStr"/>
@@ -23139,7 +23139,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -23169,7 +23169,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B694" t="inlineStr"/>
@@ -23199,7 +23199,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B695" t="inlineStr"/>
@@ -23229,7 +23229,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B696" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B697" t="inlineStr"/>
@@ -23289,7 +23289,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B698" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B699" t="inlineStr"/>
@@ -23349,7 +23349,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B700" t="inlineStr"/>
@@ -23379,7 +23379,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B701" t="inlineStr"/>
@@ -23409,7 +23409,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -23439,7 +23439,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B703" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B704" t="inlineStr"/>
@@ -23499,7 +23499,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B705" t="inlineStr"/>
@@ -23529,7 +23529,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B706" t="inlineStr"/>
@@ -23559,7 +23559,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B707" t="inlineStr"/>
@@ -23589,7 +23589,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B708" t="inlineStr"/>
@@ -23619,7 +23619,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B709" t="inlineStr"/>
@@ -23649,7 +23649,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B710" t="inlineStr"/>
@@ -23679,7 +23679,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B711" t="inlineStr"/>
@@ -23709,7 +23709,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B712" t="inlineStr"/>
@@ -23739,7 +23739,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B713" t="inlineStr"/>
@@ -23769,7 +23769,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B714" t="inlineStr"/>
@@ -23799,7 +23799,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B715" t="inlineStr"/>
@@ -23829,7 +23829,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B716" t="inlineStr"/>
@@ -23859,7 +23859,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B718" t="inlineStr"/>
@@ -23919,7 +23919,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B719" t="inlineStr"/>
@@ -23949,7 +23949,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
@@ -23979,7 +23979,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B721" t="inlineStr"/>
